--- a/data/trans_dic/P36BPD01_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,21; 95,95</t>
+          <t>92,19; 96,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,36; 95,89</t>
+          <t>93,12; 95,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,39; 95,61</t>
+          <t>93,41; 95,56</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,26; 96,39</t>
+          <t>93,2; 96,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,29; 96,74</t>
+          <t>94,36; 96,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,17; 96,12</t>
+          <t>94,09; 96,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,65</t>
+          <t>95,83; 98,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,3; 97,91</t>
+          <t>95,42; 98,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,05; 97,96</t>
+          <t>96,03; 97,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,14; 96,36</t>
+          <t>94,11; 96,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,79; 96,42</t>
+          <t>94,78; 96,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,78; 96,11</t>
+          <t>94,74; 96,13</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva</t>
+          <t>Población que utilizan como principal grasa para cocinar el aceite de oliva (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>473894; 493123</t>
+          <t>473790; 493890</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>702773; 721851</t>
+          <t>700995; 720657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1182993; 1211082</t>
+          <t>1183218; 1210444</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2121791; 2192946</t>
+          <t>2120357; 2191060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2106644; 2161380</t>
+          <t>2108170; 2162329</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4246217; 4334265</t>
+          <t>4242915; 4335131</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>617920; 636098</t>
+          <t>617868; 636137</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>629415; 646669</t>
+          <t>630228; 647290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1253731; 1278581</t>
+          <t>1253434; 1278998</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3232646; 3308830</t>
+          <t>3231490; 3306442</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3457344; 3516697</t>
+          <t>3457088; 3514302</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6711749; 6806098</t>
+          <t>6709085; 6807245</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD01_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD01_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>92,19; 96,1</t>
+          <t>90,52; 94,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,12; 95,74</t>
+          <t>92,85; 95,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93,41; 95,56</t>
+          <t>92,36; 94,77</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,2; 96,31</t>
+          <t>91,55; 94,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,36; 96,78</t>
+          <t>92,98; 95,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>94,09; 96,14</t>
+          <t>92,7; 94,37</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>95,83; 98,66</t>
+          <t>95,12; 98,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,42; 98,01</t>
+          <t>94,39; 97,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96,03; 97,99</t>
+          <t>95,55; 97,57</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,11; 96,29</t>
+          <t>92,74; 94,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,78; 96,35</t>
+          <t>93,76; 95,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,74; 96,13</t>
+          <t>93,6; 94,79</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>484941</t>
+          <t>536102</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>712261</t>
+          <t>771574</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1197202</t>
+          <t>1307675</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>473790; 493890</t>
+          <t>522791; 547454</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>700995; 720657</t>
+          <t>760558; 782733</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1183218; 1210444</t>
+          <t>1289992; 1323586</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2155002</t>
+          <t>2062702</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2133488</t>
+          <t>2038900</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4288489</t>
+          <t>4101602</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2120357; 2191060</t>
+          <t>2028900; 2091625</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2108170; 2162329</t>
+          <t>2014703; 2058984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4242915; 4335131</t>
+          <t>4063124; 4136408</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>628738</t>
+          <t>688924</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>640023</t>
+          <t>707155</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1268761</t>
+          <t>1396079</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>617868; 636137</t>
+          <t>675052; 696972</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>630228; 647290</t>
+          <t>693652; 715442</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1253434; 1278998</t>
+          <t>1380286; 1409534</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3268680</t>
+          <t>3287728</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3485771</t>
+          <t>3517629</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6754451</t>
+          <t>6805356</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3231490; 3306442</t>
+          <t>3248944; 3319811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3457088; 3514302</t>
+          <t>3488477; 3541177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6709085; 6807245</t>
+          <t>6761817; 6847974</t>
         </is>
       </c>
     </row>
